--- a/backend/data/uploads/MES/2026-07-16_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-16_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C59B756A-6E94-4654-A16B-AA42544E4261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9976A4A-61CE-4D80-A305-F7907F8F0452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{21AC8088-A5F4-49FD-953E-9768A3127FE2}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{57AD02FE-BF5C-4AC4-94B4-0DDEB96B236E}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{861F942D-937B-4052-9F81-FFAAAB18DB9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A8AF4A7-F59C-4282-A18A-37FCB1C84EA8}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-16_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-16_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9976A4A-61CE-4D80-A305-F7907F8F0452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39E0E9FA-AB9B-44ED-A0F1-AB2B71096A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{57AD02FE-BF5C-4AC4-94B4-0DDEB96B236E}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9A06769F-5A9D-4ED0-88D9-B51322A410B5}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A8AF4A7-F59C-4282-A18A-37FCB1C84EA8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7303A6C2-9272-47D5-AD2D-4422736491C9}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-16_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-16_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39E0E9FA-AB9B-44ED-A0F1-AB2B71096A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62769179-E896-466A-AA16-09F131B158F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9A06769F-5A9D-4ED0-88D9-B51322A410B5}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{8BF612AF-063A-487D-921E-E39FE8D5E03D}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7303A6C2-9272-47D5-AD2D-4422736491C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2018DC1E-6682-4E51-BCEA-F376A63D8302}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
